--- a/data/DATA_CARLA_P2.xlsx
+++ b/data/DATA_CARLA_P2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schwarz-f\Desktop\use-cases-harmonisation\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{480E8DD7-023D-4153-A753-7E30FD1E3CB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{403AF710-3332-47F0-9389-2067FE836F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9066751A-66DC-4340-90DF-5664720171E7}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9066751A-66DC-4340-90DF-5664720171E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -196,7 +196,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -231,7 +231,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -809,9 +809,7 @@
       <c r="AG2">
         <v>0</v>
       </c>
-      <c r="AH2" s="1">
-        <v>39814</v>
-      </c>
+      <c r="AH2" s="1"/>
       <c r="AI2">
         <v>0</v>
       </c>
@@ -1191,9 +1189,7 @@
       <c r="AG5">
         <v>1</v>
       </c>
-      <c r="AH5" s="1">
-        <v>39814</v>
-      </c>
+      <c r="AH5" s="1"/>
       <c r="AI5">
         <v>1</v>
       </c>
@@ -1445,9 +1441,7 @@
       <c r="AG7">
         <v>1</v>
       </c>
-      <c r="AH7" s="1">
-        <v>39814</v>
-      </c>
+      <c r="AH7" s="1"/>
       <c r="AI7">
         <v>1</v>
       </c>
